--- a/tame_output/ON/bt/strategyON_20240214.xlsx
+++ b/tame_output/ON/bt/strategyON_20240214.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.1%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>1.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>127.2%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>120.8%</t>
+          <t>120.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>1.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1872"/>
+  <dimension ref="A1:G1873"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458007309937238</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44617,6 +44617,29 @@
       </c>
       <c r="G1872" t="n">
         <v>4.466973481013184</v>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" s="2" t="n">
+        <v>45335</v>
+      </c>
+      <c r="B1873" t="n">
+        <v>3.447852901079075</v>
+      </c>
+      <c r="C1873" t="n">
+        <v>3.115605264938036</v>
+      </c>
+      <c r="D1873" t="n">
+        <v>1.618997686955725</v>
+      </c>
+      <c r="E1873" t="n">
+        <v>3.762847915406578</v>
+      </c>
+      <c r="F1873" t="n">
+        <v>2.257591006384487</v>
+      </c>
+      <c r="G1873" t="n">
+        <v>4.470159868768729</v>
       </c>
     </row>
   </sheetData>
